--- a/Termodinamica/p12_termodinamica/p12.xlsx
+++ b/Termodinamica/p12_termodinamica/p12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\proyectos\p12_termodinamica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode\practicas\Termodinamica\p12_termodinamica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7DE896-DEE7-4B4C-A67D-462C64F1A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E48C8-AF37-4FE7-B0FC-6EE23A3AFD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="1044" windowWidth="12528" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -371,7 +371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -396,14 +396,20 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <f>(ROW()-1)*15</f>
-        <v>15</v>
+        <f>(ROW()-2)*20</f>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0.1</v>
       </c>
+      <c r="C2">
+        <v>54.2</v>
+      </c>
       <c r="D2">
         <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>63.1</v>
       </c>
       <c r="F2">
         <v>0.1</v>
@@ -411,14 +417,20 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <f t="shared" ref="A3:A66" si="0">(ROW()-1)*15</f>
-        <v>30</v>
+        <f t="shared" ref="A3:A66" si="0">(ROW()-2)*20</f>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>0.1</v>
       </c>
+      <c r="C3">
+        <v>54.2</v>
+      </c>
       <c r="D3">
         <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>62.4</v>
       </c>
       <c r="F3">
         <v>0.1</v>
@@ -427,13 +439,19 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>0.1</v>
       </c>
+      <c r="C4">
+        <v>54.1</v>
+      </c>
       <c r="D4">
         <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>61.7</v>
       </c>
       <c r="F4">
         <v>0.1</v>
@@ -447,8 +465,14 @@
       <c r="B5">
         <v>0.1</v>
       </c>
+      <c r="C5">
+        <v>54</v>
+      </c>
       <c r="D5">
         <v>0.1</v>
+      </c>
+      <c r="E5">
+        <v>60.2</v>
       </c>
       <c r="F5">
         <v>0.1</v>
@@ -457,13 +481,19 @@
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>0.1</v>
       </c>
+      <c r="C6">
+        <v>53.8</v>
+      </c>
       <c r="D6">
         <v>0.1</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
       </c>
       <c r="F6">
         <v>0.1</v>
@@ -472,13 +502,19 @@
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B7">
         <v>0.1</v>
       </c>
+      <c r="C7">
+        <v>53.5</v>
+      </c>
       <c r="D7">
         <v>0.1</v>
+      </c>
+      <c r="E7">
+        <v>59.1</v>
       </c>
       <c r="F7">
         <v>0.1</v>
@@ -487,13 +523,19 @@
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B8">
         <v>0.1</v>
       </c>
+      <c r="C8">
+        <v>53.2</v>
+      </c>
       <c r="D8">
         <v>0.1</v>
+      </c>
+      <c r="E8">
+        <v>58.3</v>
       </c>
       <c r="F8">
         <v>0.1</v>
@@ -502,13 +544,19 @@
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B9">
         <v>0.1</v>
       </c>
+      <c r="C9">
+        <v>52.9</v>
+      </c>
       <c r="D9">
         <v>0.1</v>
+      </c>
+      <c r="E9">
+        <v>57.5</v>
       </c>
       <c r="F9">
         <v>0.1</v>
@@ -517,13 +565,19 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="B10">
         <v>0.1</v>
       </c>
+      <c r="C10">
+        <v>52.6</v>
+      </c>
       <c r="D10">
         <v>0.1</v>
+      </c>
+      <c r="E10">
+        <v>56.7</v>
       </c>
       <c r="F10">
         <v>0.1</v>
@@ -532,13 +586,19 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="B11">
         <v>0.1</v>
       </c>
+      <c r="C11">
+        <v>52.2</v>
+      </c>
       <c r="D11">
         <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>56.2</v>
       </c>
       <c r="F11">
         <v>0.1</v>
@@ -547,13 +607,19 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="B12">
         <v>0.1</v>
       </c>
+      <c r="C12">
+        <v>51.9</v>
+      </c>
       <c r="D12">
         <v>0.1</v>
+      </c>
+      <c r="E12">
+        <v>56.9</v>
       </c>
       <c r="F12">
         <v>0.1</v>
@@ -562,13 +628,19 @@
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="B13">
         <v>0.1</v>
       </c>
+      <c r="C13">
+        <v>51.6</v>
+      </c>
       <c r="D13">
         <v>0.1</v>
+      </c>
+      <c r="E13">
+        <v>56.5</v>
       </c>
       <c r="F13">
         <v>0.1</v>
@@ -577,13 +649,19 @@
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="B14">
         <v>0.1</v>
       </c>
+      <c r="C14">
+        <v>51.5</v>
+      </c>
       <c r="D14">
         <v>0.1</v>
+      </c>
+      <c r="E14">
+        <v>57.1</v>
       </c>
       <c r="F14">
         <v>0.1</v>
@@ -592,13 +670,19 @@
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="B15">
         <v>0.1</v>
       </c>
+      <c r="C15">
+        <v>51.4</v>
+      </c>
       <c r="D15">
         <v>0.1</v>
+      </c>
+      <c r="E15">
+        <v>58</v>
       </c>
       <c r="F15">
         <v>0.1</v>
@@ -606,14 +690,20 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <f>(ROW()-1)*15</f>
-        <v>225</v>
+        <f t="shared" si="0"/>
+        <v>280</v>
       </c>
       <c r="B16">
         <v>0.1</v>
       </c>
+      <c r="C16">
+        <v>51.5</v>
+      </c>
       <c r="D16">
         <v>0.1</v>
+      </c>
+      <c r="E16">
+        <v>58.9</v>
       </c>
       <c r="F16">
         <v>0.1</v>
@@ -622,13 +712,19 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B17">
         <v>0.1</v>
       </c>
+      <c r="C17">
+        <v>51.7</v>
+      </c>
       <c r="D17">
         <v>0.1</v>
+      </c>
+      <c r="E17">
+        <v>59.9</v>
       </c>
       <c r="F17">
         <v>0.1</v>
@@ -637,13 +733,19 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="B18">
         <v>0.1</v>
       </c>
+      <c r="C18">
+        <v>52</v>
+      </c>
       <c r="D18">
         <v>0.1</v>
+      </c>
+      <c r="E18">
+        <v>60.9</v>
       </c>
       <c r="F18">
         <v>0.1</v>
@@ -652,13 +754,19 @@
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="B19">
         <v>0.1</v>
       </c>
+      <c r="C19">
+        <v>52.3</v>
+      </c>
       <c r="D19">
         <v>0.1</v>
+      </c>
+      <c r="E19">
+        <v>62</v>
       </c>
       <c r="F19">
         <v>0.1</v>
@@ -667,13 +775,19 @@
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="B20">
         <v>0.1</v>
       </c>
+      <c r="C20">
+        <v>52.7</v>
+      </c>
       <c r="D20">
         <v>0.1</v>
+      </c>
+      <c r="E20">
+        <v>63.1</v>
       </c>
       <c r="F20">
         <v>0.1</v>
@@ -682,13 +796,19 @@
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="B21">
         <v>0.1</v>
       </c>
+      <c r="C21">
+        <v>53.1</v>
+      </c>
       <c r="D21">
         <v>0.1</v>
+      </c>
+      <c r="E21">
+        <v>63.9</v>
       </c>
       <c r="F21">
         <v>0.1</v>
@@ -697,13 +817,19 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
-        <v>315</v>
+        <v>400</v>
       </c>
       <c r="B22">
         <v>0.1</v>
       </c>
+      <c r="C22">
+        <v>53.5</v>
+      </c>
       <c r="D22">
         <v>0.1</v>
+      </c>
+      <c r="E22">
+        <v>64.3</v>
       </c>
       <c r="F22">
         <v>0.1</v>
@@ -712,13 +838,19 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="B23">
         <v>0.1</v>
       </c>
+      <c r="C23">
+        <v>53.9</v>
+      </c>
       <c r="D23">
         <v>0.1</v>
+      </c>
+      <c r="E23">
+        <v>64.400000000000006</v>
       </c>
       <c r="F23">
         <v>0.1</v>
@@ -727,13 +859,19 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
-        <v>345</v>
+        <v>440</v>
       </c>
       <c r="B24">
         <v>0.1</v>
       </c>
+      <c r="C24">
+        <v>54.1</v>
+      </c>
       <c r="D24">
         <v>0.1</v>
+      </c>
+      <c r="E24">
+        <v>64.099999999999994</v>
       </c>
       <c r="F24">
         <v>0.1</v>
@@ -742,13 +880,19 @@
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="B25">
         <v>0.1</v>
       </c>
+      <c r="C25">
+        <v>54.3</v>
+      </c>
       <c r="D25">
         <v>0.1</v>
+      </c>
+      <c r="E25">
+        <v>63.6</v>
       </c>
       <c r="F25">
         <v>0.1</v>
@@ -757,13 +901,19 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="B26">
         <v>0.1</v>
       </c>
+      <c r="C26">
+        <v>54.4</v>
+      </c>
       <c r="D26">
         <v>0.1</v>
+      </c>
+      <c r="E26">
+        <v>63</v>
       </c>
       <c r="F26">
         <v>0.1</v>
@@ -772,13 +922,19 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="B27">
         <v>0.1</v>
       </c>
+      <c r="C27">
+        <v>54.4</v>
+      </c>
       <c r="D27">
         <v>0.1</v>
+      </c>
+      <c r="E27">
+        <v>62.2</v>
       </c>
       <c r="F27">
         <v>0.1</v>
@@ -787,13 +943,19 @@
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="B28">
         <v>0.1</v>
       </c>
+      <c r="C28">
+        <v>54.3</v>
+      </c>
       <c r="D28">
         <v>0.1</v>
+      </c>
+      <c r="E28">
+        <v>61.4</v>
       </c>
       <c r="F28">
         <v>0.1</v>
@@ -802,13 +964,19 @@
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="B29">
         <v>0.1</v>
       </c>
+      <c r="C29">
+        <v>54.1</v>
+      </c>
       <c r="D29">
         <v>0.1</v>
+      </c>
+      <c r="E29">
+        <v>60.6</v>
       </c>
       <c r="F29">
         <v>0.1</v>
@@ -817,13 +985,19 @@
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
-        <v>435</v>
+        <v>560</v>
       </c>
       <c r="B30">
         <v>0.1</v>
       </c>
+      <c r="C30">
+        <v>53.9</v>
+      </c>
       <c r="D30">
         <v>0.1</v>
+      </c>
+      <c r="E30">
+        <v>59.8</v>
       </c>
       <c r="F30">
         <v>0.1</v>
@@ -832,13 +1006,19 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="B31">
         <v>0.1</v>
       </c>
+      <c r="C31">
+        <v>53.6</v>
+      </c>
       <c r="D31">
         <v>0.1</v>
+      </c>
+      <c r="E31">
+        <v>58.9</v>
       </c>
       <c r="F31">
         <v>0.1</v>
@@ -847,13 +1027,19 @@
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
-        <v>465</v>
+        <v>600</v>
       </c>
       <c r="B32">
         <v>0.1</v>
       </c>
+      <c r="C32">
+        <v>53.3</v>
+      </c>
       <c r="D32">
         <v>0.1</v>
+      </c>
+      <c r="E32">
+        <v>58</v>
       </c>
       <c r="F32">
         <v>0.1</v>
@@ -862,13 +1048,19 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>620</v>
       </c>
       <c r="B33">
         <v>0.1</v>
       </c>
+      <c r="C33">
+        <v>52.9</v>
+      </c>
       <c r="D33">
         <v>0.1</v>
+      </c>
+      <c r="E33">
+        <v>57.3</v>
       </c>
       <c r="F33">
         <v>0.1</v>
@@ -877,13 +1069,19 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
-        <v>495</v>
+        <v>640</v>
       </c>
       <c r="B34">
         <v>0.1</v>
       </c>
+      <c r="C34">
+        <v>52.6</v>
+      </c>
       <c r="D34">
         <v>0.1</v>
+      </c>
+      <c r="E34">
+        <v>56.4</v>
       </c>
       <c r="F34">
         <v>0.1</v>
@@ -892,13 +1090,19 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="0"/>
-        <v>510</v>
+        <v>660</v>
       </c>
       <c r="B35">
         <v>0.1</v>
       </c>
+      <c r="C35">
+        <v>52.2</v>
+      </c>
       <c r="D35">
         <v>0.1</v>
+      </c>
+      <c r="E35">
+        <v>56.1</v>
       </c>
       <c r="F35">
         <v>0.1</v>
@@ -907,13 +1111,19 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="0"/>
-        <v>525</v>
+        <v>680</v>
       </c>
       <c r="B36">
         <v>0.1</v>
       </c>
+      <c r="C36">
+        <v>51.9</v>
+      </c>
       <c r="D36">
         <v>0.1</v>
+      </c>
+      <c r="E36">
+        <v>56.2</v>
       </c>
       <c r="F36">
         <v>0.1</v>
@@ -922,13 +1132,19 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="B37">
         <v>0.1</v>
       </c>
+      <c r="C37">
+        <v>51.7</v>
+      </c>
       <c r="D37">
         <v>0.1</v>
+      </c>
+      <c r="E37">
+        <v>56.6</v>
       </c>
       <c r="F37">
         <v>0.1</v>
@@ -937,13 +1153,19 @@
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <f t="shared" si="0"/>
-        <v>555</v>
+        <v>720</v>
       </c>
       <c r="B38">
         <v>0.1</v>
       </c>
+      <c r="C38">
+        <v>51.6</v>
+      </c>
       <c r="D38">
         <v>0.1</v>
+      </c>
+      <c r="E38">
+        <v>57.3</v>
       </c>
       <c r="F38">
         <v>0.1</v>
@@ -952,13 +1174,19 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <f t="shared" si="0"/>
-        <v>570</v>
+        <v>740</v>
       </c>
       <c r="B39">
         <v>0.1</v>
       </c>
+      <c r="C39">
+        <v>51.6</v>
+      </c>
       <c r="D39">
         <v>0.1</v>
+      </c>
+      <c r="E39">
+        <v>58.2</v>
       </c>
       <c r="F39">
         <v>0.1</v>
@@ -967,13 +1195,19 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="0"/>
-        <v>585</v>
+        <v>760</v>
       </c>
       <c r="B40">
         <v>0.1</v>
       </c>
+      <c r="C40">
+        <v>51.7</v>
+      </c>
       <c r="D40">
         <v>0.1</v>
+      </c>
+      <c r="E40">
+        <v>59.2</v>
       </c>
       <c r="F40">
         <v>0.1</v>
@@ -982,13 +1216,19 @@
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="B41">
         <v>0.1</v>
       </c>
+      <c r="C41">
+        <v>51.9</v>
+      </c>
       <c r="D41">
         <v>0.1</v>
+      </c>
+      <c r="E41">
+        <v>60.3</v>
       </c>
       <c r="F41">
         <v>0.1</v>
@@ -997,13 +1237,19 @@
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="0"/>
-        <v>615</v>
+        <v>800</v>
       </c>
       <c r="B42">
         <v>0.1</v>
       </c>
+      <c r="C42">
+        <v>52.2</v>
+      </c>
       <c r="D42">
         <v>0.1</v>
+      </c>
+      <c r="E42">
+        <v>61.3</v>
       </c>
       <c r="F42">
         <v>0.1</v>
@@ -1012,13 +1258,19 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>820</v>
       </c>
       <c r="B43">
         <v>0.1</v>
       </c>
+      <c r="C43">
+        <v>52.5</v>
+      </c>
       <c r="D43">
         <v>0.1</v>
+      </c>
+      <c r="E43">
+        <v>62.4</v>
       </c>
       <c r="F43">
         <v>0.1</v>
@@ -1027,13 +1279,19 @@
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="0"/>
-        <v>645</v>
+        <v>840</v>
       </c>
       <c r="B44">
         <v>0.1</v>
       </c>
+      <c r="C44">
+        <v>52.9</v>
+      </c>
       <c r="D44">
         <v>0.1</v>
+      </c>
+      <c r="E44">
+        <v>63.5</v>
       </c>
       <c r="F44">
         <v>0.1</v>
@@ -1042,13 +1300,19 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>860</v>
       </c>
       <c r="B45">
         <v>0.1</v>
       </c>
+      <c r="C45">
+        <v>53.3</v>
+      </c>
       <c r="D45">
         <v>0.1</v>
+      </c>
+      <c r="E45">
+        <v>64.2</v>
       </c>
       <c r="F45">
         <v>0.1</v>
@@ -1057,13 +1321,19 @@
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="0"/>
-        <v>675</v>
+        <v>880</v>
       </c>
       <c r="B46">
         <v>0.1</v>
       </c>
+      <c r="C46">
+        <v>53.7</v>
+      </c>
       <c r="D46">
         <v>0.1</v>
+      </c>
+      <c r="E46">
+        <v>64.3</v>
       </c>
       <c r="F46">
         <v>0.1</v>
@@ -1072,13 +1342,19 @@
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="B47">
         <v>0.1</v>
       </c>
+      <c r="C47">
+        <v>54.1</v>
+      </c>
       <c r="D47">
         <v>0.1</v>
+      </c>
+      <c r="E47">
+        <v>64.5</v>
       </c>
       <c r="F47">
         <v>0.1</v>
@@ -1087,13 +1363,19 @@
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="0"/>
-        <v>705</v>
+        <v>920</v>
       </c>
       <c r="B48">
         <v>0.1</v>
       </c>
+      <c r="C48">
+        <v>54.3</v>
+      </c>
       <c r="D48">
         <v>0.1</v>
+      </c>
+      <c r="E48">
+        <v>64.2</v>
       </c>
       <c r="F48">
         <v>0.1</v>
@@ -1102,13 +1384,19 @@
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>940</v>
       </c>
       <c r="B49">
         <v>0.1</v>
       </c>
+      <c r="C49">
+        <v>54.5</v>
+      </c>
       <c r="D49">
         <v>0.1</v>
+      </c>
+      <c r="E49">
+        <v>63.7</v>
       </c>
       <c r="F49">
         <v>0.1</v>
@@ -1117,13 +1405,19 @@
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="0"/>
-        <v>735</v>
+        <v>960</v>
       </c>
       <c r="B50">
         <v>0.1</v>
       </c>
+      <c r="C50">
+        <v>54.5</v>
+      </c>
       <c r="D50">
         <v>0.1</v>
+      </c>
+      <c r="E50">
+        <v>63</v>
       </c>
       <c r="F50">
         <v>0.1</v>
@@ -1132,13 +1426,19 @@
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>980</v>
       </c>
       <c r="B51">
         <v>0.1</v>
       </c>
+      <c r="C51">
+        <v>54.4</v>
+      </c>
       <c r="D51">
         <v>0.1</v>
+      </c>
+      <c r="E51">
+        <v>62.2</v>
       </c>
       <c r="F51">
         <v>0.1</v>
@@ -1147,13 +1447,19 @@
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="0"/>
-        <v>765</v>
+        <v>1000</v>
       </c>
       <c r="B52">
         <v>0.1</v>
       </c>
+      <c r="C52">
+        <v>54.4</v>
+      </c>
       <c r="D52">
         <v>0.1</v>
+      </c>
+      <c r="E52">
+        <v>61.4</v>
       </c>
       <c r="F52">
         <v>0.1</v>
@@ -1162,13 +1468,19 @@
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>1020</v>
       </c>
       <c r="B53">
         <v>0.1</v>
       </c>
+      <c r="C53">
+        <v>54.2</v>
+      </c>
       <c r="D53">
         <v>0.1</v>
+      </c>
+      <c r="E53">
+        <v>60.5</v>
       </c>
       <c r="F53">
         <v>0.1</v>
@@ -1177,13 +1489,19 @@
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="0"/>
-        <v>795</v>
+        <v>1040</v>
       </c>
       <c r="B54">
         <v>0.1</v>
       </c>
+      <c r="C54">
+        <v>53.9</v>
+      </c>
       <c r="D54">
         <v>0.1</v>
+      </c>
+      <c r="E54">
+        <v>59.7</v>
       </c>
       <c r="F54">
         <v>0.1</v>
@@ -1192,13 +1510,19 @@
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>1060</v>
       </c>
       <c r="B55">
         <v>0.1</v>
       </c>
+      <c r="C55">
+        <v>53.7</v>
+      </c>
       <c r="D55">
         <v>0.1</v>
+      </c>
+      <c r="E55">
+        <v>58.8</v>
       </c>
       <c r="F55">
         <v>0.1</v>
@@ -1207,13 +1531,19 @@
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>1080</v>
       </c>
       <c r="B56">
         <v>0.1</v>
       </c>
+      <c r="C56">
+        <v>53.4</v>
+      </c>
       <c r="D56">
         <v>0.1</v>
+      </c>
+      <c r="E56">
+        <v>58</v>
       </c>
       <c r="F56">
         <v>0.1</v>
@@ -1222,13 +1552,19 @@
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>1100</v>
       </c>
       <c r="B57">
         <v>0.1</v>
       </c>
+      <c r="C57">
+        <v>53</v>
+      </c>
       <c r="D57">
         <v>0.1</v>
+      </c>
+      <c r="E57">
+        <v>57.2</v>
       </c>
       <c r="F57">
         <v>0.1</v>
@@ -1237,13 +1573,19 @@
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>1120</v>
       </c>
       <c r="B58">
         <v>0.1</v>
       </c>
+      <c r="C58">
+        <v>52.7</v>
+      </c>
       <c r="D58">
         <v>0.1</v>
+      </c>
+      <c r="E58">
+        <v>56.6</v>
       </c>
       <c r="F58">
         <v>0.1</v>
@@ -1252,13 +1594,19 @@
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>1140</v>
       </c>
       <c r="B59">
         <v>0.1</v>
       </c>
+      <c r="C59">
+        <v>52.3</v>
+      </c>
       <c r="D59">
         <v>0.1</v>
+      </c>
+      <c r="E59">
+        <v>56.3</v>
       </c>
       <c r="F59">
         <v>0.1</v>
@@ -1267,13 +1615,19 @@
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="0"/>
-        <v>885</v>
+        <v>1160</v>
       </c>
       <c r="B60">
         <v>0.1</v>
       </c>
+      <c r="C60">
+        <v>52</v>
+      </c>
       <c r="D60">
         <v>0.1</v>
+      </c>
+      <c r="E60">
+        <v>56.4</v>
       </c>
       <c r="F60">
         <v>0.1</v>
@@ -1282,13 +1636,19 @@
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>1180</v>
       </c>
       <c r="B61">
         <v>0.1</v>
       </c>
+      <c r="C61">
+        <v>51.8</v>
+      </c>
       <c r="D61">
         <v>0.1</v>
+      </c>
+      <c r="E61">
+        <v>57</v>
       </c>
       <c r="F61">
         <v>0.1</v>
@@ -1297,13 +1657,19 @@
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="0"/>
-        <v>915</v>
+        <v>1200</v>
       </c>
       <c r="B62">
         <v>0.1</v>
       </c>
+      <c r="C62">
+        <v>51.7</v>
+      </c>
       <c r="D62">
         <v>0.1</v>
+      </c>
+      <c r="E62">
+        <v>57.7</v>
       </c>
       <c r="F62">
         <v>0.1</v>
@@ -1312,13 +1678,19 @@
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>1220</v>
       </c>
       <c r="B63">
         <v>0.1</v>
       </c>
+      <c r="C63">
+        <v>51.8</v>
+      </c>
       <c r="D63">
         <v>0.1</v>
+      </c>
+      <c r="E63">
+        <v>58.6</v>
       </c>
       <c r="F63">
         <v>0.1</v>
@@ -1327,13 +1699,19 @@
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="0"/>
-        <v>945</v>
+        <v>1240</v>
       </c>
       <c r="B64">
         <v>0.1</v>
       </c>
+      <c r="C64">
+        <v>51.9</v>
+      </c>
       <c r="D64">
         <v>0.1</v>
+      </c>
+      <c r="E64">
+        <v>59.6</v>
       </c>
       <c r="F64">
         <v>0.1</v>
@@ -1342,13 +1720,19 @@
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1260</v>
       </c>
       <c r="B65">
         <v>0.1</v>
       </c>
+      <c r="C65">
+        <v>52.1</v>
+      </c>
       <c r="D65">
         <v>0.1</v>
+      </c>
+      <c r="E65">
+        <v>60.7</v>
       </c>
       <c r="F65">
         <v>0.1</v>
@@ -1357,13 +1741,19 @@
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="0"/>
-        <v>975</v>
+        <v>1280</v>
       </c>
       <c r="B66">
         <v>0.1</v>
       </c>
+      <c r="C66">
+        <v>52.4</v>
+      </c>
       <c r="D66">
         <v>0.1</v>
+      </c>
+      <c r="E66">
+        <v>61.8</v>
       </c>
       <c r="F66">
         <v>0.1</v>
@@ -1371,14 +1761,20 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <f t="shared" ref="A67:A117" si="1">(ROW()-1)*15</f>
-        <v>990</v>
+        <f t="shared" ref="A67:A92" si="1">(ROW()-2)*20</f>
+        <v>1300</v>
       </c>
       <c r="B67">
         <v>0.1</v>
       </c>
+      <c r="C67">
+        <v>52.8</v>
+      </c>
       <c r="D67">
         <v>0.1</v>
+      </c>
+      <c r="E67">
+        <v>62.9</v>
       </c>
       <c r="F67">
         <v>0.1</v>
@@ -1387,13 +1783,19 @@
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="1"/>
-        <v>1005</v>
+        <v>1320</v>
       </c>
       <c r="B68">
         <v>0.1</v>
       </c>
+      <c r="C68">
+        <v>53.2</v>
+      </c>
       <c r="D68">
         <v>0.1</v>
+      </c>
+      <c r="E68">
+        <v>63.8</v>
       </c>
       <c r="F68">
         <v>0.1</v>
@@ -1402,13 +1804,19 @@
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>1340</v>
       </c>
       <c r="B69">
         <v>0.1</v>
       </c>
+      <c r="C69">
+        <v>53.6</v>
+      </c>
       <c r="D69">
         <v>0.1</v>
+      </c>
+      <c r="E69">
+        <v>64.5</v>
       </c>
       <c r="F69">
         <v>0.1</v>
@@ -1417,13 +1825,19 @@
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>1360</v>
       </c>
       <c r="B70">
         <v>0.1</v>
       </c>
+      <c r="C70">
+        <v>54</v>
+      </c>
       <c r="D70">
         <v>0.1</v>
+      </c>
+      <c r="E70">
+        <v>64.8</v>
       </c>
       <c r="F70">
         <v>0.1</v>
@@ -1432,13 +1846,19 @@
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="1"/>
-        <v>1050</v>
+        <v>1380</v>
       </c>
       <c r="B71">
         <v>0.1</v>
       </c>
+      <c r="C71">
+        <v>54.3</v>
+      </c>
       <c r="D71">
         <v>0.1</v>
+      </c>
+      <c r="E71">
+        <v>64.599999999999994</v>
       </c>
       <c r="F71">
         <v>0.1</v>
@@ -1447,13 +1867,19 @@
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="1"/>
-        <v>1065</v>
+        <v>1400</v>
       </c>
       <c r="B72">
         <v>0.1</v>
       </c>
+      <c r="C72">
+        <v>54.5</v>
+      </c>
       <c r="D72">
         <v>0.1</v>
+      </c>
+      <c r="E72">
+        <v>64.2</v>
       </c>
       <c r="F72">
         <v>0.1</v>
@@ -1462,13 +1888,19 @@
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>1420</v>
       </c>
       <c r="B73">
         <v>0.1</v>
       </c>
+      <c r="C73">
+        <v>54.6</v>
+      </c>
       <c r="D73">
         <v>0.1</v>
+      </c>
+      <c r="E73">
+        <v>63.6</v>
       </c>
       <c r="F73">
         <v>0.1</v>
@@ -1477,13 +1909,19 @@
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="1"/>
-        <v>1095</v>
+        <v>1440</v>
       </c>
       <c r="B74">
         <v>0.1</v>
       </c>
+      <c r="C74">
+        <v>54.7</v>
+      </c>
       <c r="D74">
         <v>0.1</v>
+      </c>
+      <c r="E74">
+        <v>62.9</v>
       </c>
       <c r="F74">
         <v>0.1</v>
@@ -1492,13 +1930,19 @@
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>1460</v>
       </c>
       <c r="B75">
         <v>0.1</v>
       </c>
+      <c r="C75">
+        <v>54.6</v>
+      </c>
       <c r="D75">
         <v>0.1</v>
+      </c>
+      <c r="E75">
+        <v>62.1</v>
       </c>
       <c r="F75">
         <v>0.1</v>
@@ -1507,13 +1951,19 @@
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="1"/>
-        <v>1125</v>
+        <v>1480</v>
       </c>
       <c r="B76">
         <v>0.1</v>
       </c>
+      <c r="C76">
+        <v>54.4</v>
+      </c>
       <c r="D76">
         <v>0.1</v>
+      </c>
+      <c r="E76">
+        <v>61.3</v>
       </c>
       <c r="F76">
         <v>0.1</v>
@@ -1522,13 +1972,19 @@
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="1"/>
-        <v>1140</v>
+        <v>1500</v>
       </c>
       <c r="B77">
         <v>0.1</v>
       </c>
+      <c r="C77">
+        <v>54.3</v>
+      </c>
       <c r="D77">
         <v>0.1</v>
+      </c>
+      <c r="E77">
+        <v>60.5</v>
       </c>
       <c r="F77">
         <v>0.1</v>
@@ -1537,13 +1993,19 @@
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="1"/>
-        <v>1155</v>
+        <v>1520</v>
       </c>
       <c r="B78">
         <v>0.1</v>
       </c>
+      <c r="C78">
+        <v>54</v>
+      </c>
       <c r="D78">
         <v>0.1</v>
+      </c>
+      <c r="E78">
+        <v>59.7</v>
       </c>
       <c r="F78">
         <v>0.1</v>
@@ -1552,13 +2014,19 @@
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <f t="shared" si="1"/>
-        <v>1170</v>
+        <v>1540</v>
       </c>
       <c r="B79">
         <v>0.1</v>
       </c>
+      <c r="C79">
+        <v>53.7</v>
+      </c>
       <c r="D79">
         <v>0.1</v>
+      </c>
+      <c r="E79">
+        <v>58.8</v>
       </c>
       <c r="F79">
         <v>0.1</v>
@@ -1567,13 +2035,19 @@
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <f t="shared" si="1"/>
-        <v>1185</v>
+        <v>1560</v>
       </c>
       <c r="B80">
         <v>0.1</v>
       </c>
+      <c r="C80">
+        <v>53.4</v>
+      </c>
       <c r="D80">
         <v>0.1</v>
+      </c>
+      <c r="E80">
+        <v>57.8</v>
       </c>
       <c r="F80">
         <v>0.1</v>
@@ -1582,13 +2056,19 @@
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1580</v>
       </c>
       <c r="B81">
         <v>0.1</v>
       </c>
+      <c r="C81">
+        <v>53</v>
+      </c>
       <c r="D81">
         <v>0.1</v>
+      </c>
+      <c r="E81">
+        <v>57.2</v>
       </c>
       <c r="F81">
         <v>0.1</v>
@@ -1597,13 +2077,19 @@
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <f t="shared" si="1"/>
-        <v>1215</v>
+        <v>1600</v>
       </c>
       <c r="B82">
         <v>0.1</v>
       </c>
+      <c r="C82">
+        <v>52.7</v>
+      </c>
       <c r="D82">
         <v>0.1</v>
+      </c>
+      <c r="E82">
+        <v>56.6</v>
       </c>
       <c r="F82">
         <v>0.1</v>
@@ -1612,13 +2098,19 @@
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="1"/>
-        <v>1230</v>
+        <v>1620</v>
       </c>
       <c r="B83">
         <v>0.1</v>
       </c>
+      <c r="C83">
+        <v>52.3</v>
+      </c>
       <c r="D83">
         <v>0.1</v>
+      </c>
+      <c r="E83">
+        <v>56.4</v>
       </c>
       <c r="F83">
         <v>0.1</v>
@@ -1627,13 +2119,19 @@
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" si="1"/>
-        <v>1245</v>
+        <v>1640</v>
       </c>
       <c r="B84">
         <v>0.1</v>
       </c>
+      <c r="C84">
+        <v>52.1</v>
+      </c>
       <c r="D84">
         <v>0.1</v>
+      </c>
+      <c r="E84">
+        <v>56.7</v>
       </c>
       <c r="F84">
         <v>0.1</v>
@@ -1642,13 +2140,19 @@
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="1"/>
-        <v>1260</v>
+        <v>1660</v>
       </c>
       <c r="B85">
         <v>0.1</v>
       </c>
+      <c r="C85">
+        <v>51.9</v>
+      </c>
       <c r="D85">
         <v>0.1</v>
+      </c>
+      <c r="E85">
+        <v>57.2</v>
       </c>
       <c r="F85">
         <v>0.1</v>
@@ -1657,13 +2161,19 @@
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="1"/>
-        <v>1275</v>
+        <v>1680</v>
       </c>
       <c r="B86">
         <v>0.1</v>
       </c>
+      <c r="C86">
+        <v>51.9</v>
+      </c>
       <c r="D86">
         <v>0.1</v>
+      </c>
+      <c r="E86">
+        <v>58.1</v>
       </c>
       <c r="F86">
         <v>0.1</v>
@@ -1672,13 +2182,19 @@
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="1"/>
-        <v>1290</v>
+        <v>1700</v>
       </c>
       <c r="B87">
         <v>0.1</v>
       </c>
+      <c r="C87">
+        <v>51.9</v>
+      </c>
       <c r="D87">
         <v>0.1</v>
+      </c>
+      <c r="E87">
+        <v>59</v>
       </c>
       <c r="F87">
         <v>0.1</v>
@@ -1687,13 +2203,19 @@
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="1"/>
-        <v>1305</v>
+        <v>1720</v>
       </c>
       <c r="B88">
         <v>0.1</v>
       </c>
+      <c r="C88">
+        <v>52.1</v>
+      </c>
       <c r="D88">
         <v>0.1</v>
+      </c>
+      <c r="E88">
+        <v>60</v>
       </c>
       <c r="F88">
         <v>0.1</v>
@@ -1702,13 +2224,19 @@
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1740</v>
       </c>
       <c r="B89">
         <v>0.1</v>
       </c>
+      <c r="C89">
+        <v>52.3</v>
+      </c>
       <c r="D89">
         <v>0.1</v>
+      </c>
+      <c r="E89">
+        <v>61.2</v>
       </c>
       <c r="F89">
         <v>0.1</v>
@@ -1717,13 +2245,19 @@
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="1"/>
-        <v>1335</v>
+        <v>1760</v>
       </c>
       <c r="B90">
         <v>0.1</v>
       </c>
+      <c r="C90">
+        <v>52.7</v>
+      </c>
       <c r="D90">
         <v>0.1</v>
+      </c>
+      <c r="E90">
+        <v>62.3</v>
       </c>
       <c r="F90">
         <v>0.1</v>
@@ -1732,13 +2266,19 @@
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="1"/>
-        <v>1350</v>
+        <v>1780</v>
       </c>
       <c r="B91">
         <v>0.1</v>
       </c>
+      <c r="C91">
+        <v>53</v>
+      </c>
       <c r="D91">
         <v>0.1</v>
+      </c>
+      <c r="E91">
+        <v>63.4</v>
       </c>
       <c r="F91">
         <v>0.1</v>
@@ -1747,270 +2287,21 @@
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="1"/>
-        <v>1365</v>
+        <v>1800</v>
       </c>
       <c r="B92">
         <v>0.1</v>
       </c>
+      <c r="C92">
+        <v>53.5</v>
+      </c>
       <c r="D92">
         <v>0.1</v>
       </c>
+      <c r="E92">
+        <v>64.3</v>
+      </c>
       <c r="F92">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <f t="shared" si="1"/>
-        <v>1380</v>
-      </c>
-      <c r="B93">
-        <v>0.1</v>
-      </c>
-      <c r="D93">
-        <v>0.1</v>
-      </c>
-      <c r="F93">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <f t="shared" si="1"/>
-        <v>1395</v>
-      </c>
-      <c r="B94">
-        <v>0.1</v>
-      </c>
-      <c r="D94">
-        <v>0.1</v>
-      </c>
-      <c r="F94">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <f t="shared" si="1"/>
-        <v>1410</v>
-      </c>
-      <c r="B95">
-        <v>0.1</v>
-      </c>
-      <c r="D95">
-        <v>0.1</v>
-      </c>
-      <c r="F95">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <f t="shared" si="1"/>
-        <v>1425</v>
-      </c>
-      <c r="B96">
-        <v>0.1</v>
-      </c>
-      <c r="D96">
-        <v>0.1</v>
-      </c>
-      <c r="F96">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <f t="shared" si="1"/>
-        <v>1440</v>
-      </c>
-      <c r="B97">
-        <v>0.1</v>
-      </c>
-      <c r="D97">
-        <v>0.1</v>
-      </c>
-      <c r="F97">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <f t="shared" si="1"/>
-        <v>1455</v>
-      </c>
-      <c r="B98">
-        <v>0.1</v>
-      </c>
-      <c r="D98">
-        <v>0.1</v>
-      </c>
-      <c r="F98">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <f t="shared" si="1"/>
-        <v>1470</v>
-      </c>
-      <c r="B99">
-        <v>0.1</v>
-      </c>
-      <c r="D99">
-        <v>0.1</v>
-      </c>
-      <c r="F99">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <f t="shared" si="1"/>
-        <v>1485</v>
-      </c>
-      <c r="B100">
-        <v>0.1</v>
-      </c>
-      <c r="D100">
-        <v>0.1</v>
-      </c>
-      <c r="F100">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <f t="shared" si="1"/>
-        <v>1500</v>
-      </c>
-      <c r="B101">
-        <v>0.1</v>
-      </c>
-      <c r="D101">
-        <v>0.1</v>
-      </c>
-      <c r="F101">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <f t="shared" si="1"/>
-        <v>1515</v>
-      </c>
-      <c r="B102">
-        <v>0.1</v>
-      </c>
-      <c r="D102">
-        <v>0.1</v>
-      </c>
-      <c r="F102">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <f t="shared" si="1"/>
-        <v>1530</v>
-      </c>
-      <c r="B103">
-        <v>0.1</v>
-      </c>
-      <c r="D103">
-        <v>0.1</v>
-      </c>
-      <c r="F103">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <f t="shared" si="1"/>
-        <v>1545</v>
-      </c>
-      <c r="B104">
-        <v>0.1</v>
-      </c>
-      <c r="D104">
-        <v>0.1</v>
-      </c>
-      <c r="F104">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <f t="shared" si="1"/>
-        <v>1560</v>
-      </c>
-      <c r="B105">
-        <v>0.1</v>
-      </c>
-      <c r="D105">
-        <v>0.1</v>
-      </c>
-      <c r="F105">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <f t="shared" si="1"/>
-        <v>1575</v>
-      </c>
-      <c r="B106">
-        <v>0.1</v>
-      </c>
-      <c r="D106">
-        <v>0.1</v>
-      </c>
-      <c r="F106">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <f t="shared" si="1"/>
-        <v>1590</v>
-      </c>
-      <c r="B107">
-        <v>0.1</v>
-      </c>
-      <c r="D107">
-        <v>0.1</v>
-      </c>
-      <c r="F107">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <f t="shared" si="1"/>
-        <v>1605</v>
-      </c>
-      <c r="B108">
-        <v>0.1</v>
-      </c>
-      <c r="D108">
-        <v>0.1</v>
-      </c>
-      <c r="F108">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <f t="shared" si="1"/>
-        <v>1620</v>
-      </c>
-      <c r="B109">
-        <v>0.1</v>
-      </c>
-      <c r="D109">
-        <v>0.1</v>
-      </c>
-      <c r="F109">
         <v>0.1</v>
       </c>
     </row>

--- a/Termodinamica/p12_termodinamica/p12.xlsx
+++ b/Termodinamica/p12_termodinamica/p12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode\practicas\Termodinamica\p12_termodinamica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vscode\practicas\Practicas-Fisica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507E48C8-AF37-4FE7-B0FC-6EE23A3AFD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F57CE56-004D-43D0-8D43-50BBA7870A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="1044" windowWidth="12528" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
